--- a/media/datasets/sample_2.xlsx
+++ b/media/datasets/sample_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2db839eea69b881e/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{1B76C8D6-EFBC-4FA5-A1F5-BA7F69DA8648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758074E4-287D-4182-B4BF-95817B629C12}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{1B76C8D6-EFBC-4FA5-A1F5-BA7F69DA8648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64292AB6-3525-4874-A743-D13127E089FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73F0AA5D-097F-4049-8B8C-751E8DF2236F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
   <si>
     <t>Sales</t>
   </si>
@@ -70,6 +70,30 @@
   </si>
   <si>
     <t>Accessories</t>
+  </si>
+  <si>
+    <t>Phones</t>
+  </si>
+  <si>
+    <t>tripod</t>
+  </si>
+  <si>
+    <t>gadgets</t>
+  </si>
+  <si>
+    <t>earpodes</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>ipad</t>
+  </si>
+  <si>
+    <t>speaker</t>
+  </si>
+  <si>
+    <t>headphone</t>
   </si>
 </sst>
 </file>
@@ -150,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -163,6 +187,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -483,9 +510,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4591231-F371-4B58-9970-19CBE090CC94}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -524,7 +552,7 @@
         <v>750000</v>
       </c>
       <c r="E2" s="4">
-        <v>46106</v>
+        <v>46078</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
@@ -564,7 +592,7 @@
         <v>25000</v>
       </c>
       <c r="E4" s="4">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -584,10 +612,370 @@
         <v>200000</v>
       </c>
       <c r="E5" s="4">
-        <v>46135</v>
+        <v>46126</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>50000</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46127</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1">
+        <v>650000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46137</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>70</v>
+      </c>
+      <c r="D8" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46138</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>100000</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46139</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46153</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>150000</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1">
+        <v>15</v>
+      </c>
+      <c r="D13" s="1">
+        <v>25000</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46143</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1">
+        <v>35000</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46175</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46206</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E16" s="6">
+        <v>46238</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1">
+        <v>250000</v>
+      </c>
+      <c r="E17" s="6">
+        <v>46270</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1">
+        <v>75000</v>
+      </c>
+      <c r="E18" s="6">
+        <v>46087</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1">
+        <v>25000</v>
+      </c>
+      <c r="E19" s="6">
+        <v>46302</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>75000</v>
+      </c>
+      <c r="E20" s="6">
+        <v>46364</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1">
+        <v>15000</v>
+      </c>
+      <c r="E21" s="6">
+        <v>46335</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1">
+        <v>18000</v>
+      </c>
+      <c r="E22" s="6">
+        <v>46244</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1">
+        <v>25000</v>
+      </c>
+      <c r="E23" s="6">
+        <v>46214</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
